--- a/exports/tests/data/OPD000001_metadata.xlsx
+++ b/exports/tests/data/OPD000001_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lg10/Workspace/git/fork/omicspred_backend/exports/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313BB3E9-B10F-9844-833F-D129B3128E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A05FBB-6CF6-CF45-9E0B-956134054AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5360" yWindow="3400" windowWidth="19340" windowHeight="10740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30860" yWindow="4020" windowWidth="21800" windowHeight="10740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Publication" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="95">
   <si>
     <t>OmicsPred Publication (OPP) ID</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>DS1</t>
+  </si>
+  <si>
+    <t>phi</t>
   </si>
 </sst>
 </file>
@@ -871,13 +874,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
+    <col min="8" max="8" width="9.1640625" customWidth="1"/>
+    <col min="9" max="9" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -903,31 +908,34 @@
         <v>52</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -949,19 +957,19 @@
       <c r="H2">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>65</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>66</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>63</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>62</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>40</v>
       </c>
     </row>
@@ -974,6 +982,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
